--- a/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/дв 01,09,26 млрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/дв 01,09,26 млрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\01,09,26 Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\СЫРЫ перемещение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8770CE-7853-4246-B166-D5BA55F02904}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE76008E-EB82-4DE1-98BC-BED753E1BFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AF$53</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -390,7 +382,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,6 +423,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -467,7 +465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -484,6 +482,7 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -787,6 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AW500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -805,7 +805,8 @@
     <col min="21" max="30" width="6" customWidth="1"/>
     <col min="31" max="31" width="55.5703125" customWidth="1"/>
     <col min="32" max="32" width="7" customWidth="1"/>
-    <col min="33" max="49" width="3" customWidth="1"/>
+    <col min="33" max="33" width="6.7109375" customWidth="1"/>
+    <col min="34" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -1025,7 +1026,7 @@
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1102,7 +1103,7 @@
       <c r="AV4" s="1"/>
       <c r="AW4" s="1"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1216,7 +1217,7 @@
       <c r="AV5" s="1"/>
       <c r="AW5" s="1"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1622,7 +1623,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG9" s="1"/>
+      <c r="AG9" s="1">
+        <f>F9*G9</f>
+        <v>32.524000000000001</v>
+      </c>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -1726,7 +1730,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="1"/>
+      <c r="AG10" s="16">
+        <f t="shared" ref="AG10:AG12" si="7">F10*G10</f>
+        <v>124.4995</v>
+      </c>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -1744,7 +1751,7 @@
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1830,7 +1837,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG11" s="1"/>
+      <c r="AG11" s="1">
+        <f t="shared" si="7"/>
+        <v>127.968</v>
+      </c>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -1934,7 +1944,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="1"/>
+      <c r="AG12" s="16">
+        <f t="shared" si="7"/>
+        <v>324.38400000000001</v>
+      </c>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -1952,7 +1965,7 @@
       <c r="AV12" s="1"/>
       <c r="AW12" s="1"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>43</v>
       </c>
@@ -2060,7 +2073,7 @@
       <c r="AV13" s="1"/>
       <c r="AW13" s="1"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
@@ -2100,7 +2113,7 @@
         <v>29.4</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" ref="Q14:Q36" si="7">15*P14-O14-F14</f>
+        <f t="shared" ref="Q14:Q36" si="8">15*P14-O14-F14</f>
         <v>132</v>
       </c>
       <c r="R14" s="5">
@@ -2168,7 +2181,7 @@
       <c r="AV14" s="1"/>
       <c r="AW14" s="1"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -2210,7 +2223,7 @@
         <v>3</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="R15" s="5">
@@ -2280,7 +2293,7 @@
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
@@ -2324,7 +2337,7 @@
         <v>13.8</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="R16" s="5">
@@ -2392,7 +2405,7 @@
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -2588,7 +2601,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="1"/>
+      <c r="AG18" s="1">
+        <f>F18*G18</f>
+        <v>13.600000000000001</v>
+      </c>
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
@@ -2606,7 +2622,7 @@
       <c r="AV18" s="1"/>
       <c r="AW18" s="1"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -2648,7 +2664,7 @@
         <v>3.2</v>
       </c>
       <c r="Q19" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="R19" s="5">
@@ -2716,7 +2732,7 @@
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>51</v>
       </c>
@@ -2828,7 +2844,7 @@
       <c r="AV20" s="1"/>
       <c r="AW20" s="1"/>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
@@ -3028,7 +3044,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG22" s="1"/>
+      <c r="AG22" s="1">
+        <f>F22*G22</f>
+        <v>25.200000000000003</v>
+      </c>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -3046,7 +3065,7 @@
       <c r="AV22" s="1"/>
       <c r="AW22" s="1"/>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -3086,7 +3105,7 @@
         <v>3</v>
       </c>
       <c r="Q23" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="R23" s="5">
@@ -3242,7 +3261,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG24" s="1"/>
+      <c r="AG24" s="1">
+        <f t="shared" ref="AG24:AG26" si="9">F24*G24</f>
+        <v>13.139999999999999</v>
+      </c>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
@@ -3342,7 +3364,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG25" s="1"/>
+      <c r="AG25" s="1">
+        <f t="shared" si="9"/>
+        <v>29.8</v>
+      </c>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
@@ -3442,7 +3467,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG26" s="1"/>
+      <c r="AG26" s="1">
+        <f t="shared" si="9"/>
+        <v>17.07</v>
+      </c>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
@@ -3560,7 +3588,7 @@
       <c r="AV27" s="1"/>
       <c r="AW27" s="1"/>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>60</v>
       </c>
@@ -3600,7 +3628,7 @@
         <v>15.6</v>
       </c>
       <c r="Q28" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="R28" s="5">
@@ -3668,7 +3696,7 @@
       <c r="AV28" s="1"/>
       <c r="AW28" s="1"/>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>61</v>
       </c>
@@ -3772,7 +3800,7 @@
       <c r="AV29" s="1"/>
       <c r="AW29" s="1"/>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -3967,7 +3995,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG31" s="1"/>
+      <c r="AG31" s="1">
+        <f>F31*G31</f>
+        <v>18</v>
+      </c>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
@@ -3985,7 +4016,7 @@
       <c r="AV31" s="1"/>
       <c r="AW31" s="1"/>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>64</v>
       </c>
@@ -4091,7 +4122,7 @@
       <c r="AV32" s="1"/>
       <c r="AW32" s="1"/>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -4131,7 +4162,7 @@
         <v>37</v>
       </c>
       <c r="Q33" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="R33" s="5">
@@ -4199,7 +4230,7 @@
       <c r="AV33" s="1"/>
       <c r="AW33" s="1"/>
     </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -4239,7 +4270,7 @@
         <v>25.4</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>160</v>
       </c>
       <c r="R34" s="15">
@@ -4308,7 +4339,7 @@
       <c r="AV34" s="1"/>
       <c r="AW34" s="1"/>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>67</v>
       </c>
@@ -4420,7 +4451,7 @@
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>68</v>
       </c>
@@ -4462,7 +4493,7 @@
         <v>44.2</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>227</v>
       </c>
       <c r="R36" s="5">
@@ -4530,7 +4561,7 @@
       <c r="AV36" s="1"/>
       <c r="AW36" s="1"/>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>69</v>
       </c>
@@ -4570,7 +4601,7 @@
         <v>29</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" ref="Q37:Q38" si="8">14*P37-O37-F37</f>
+        <f t="shared" ref="Q37:Q38" si="10">14*P37-O37-F37</f>
         <v>194.08199999999999</v>
       </c>
       <c r="R37" s="5">
@@ -4638,7 +4669,7 @@
       <c r="AV37" s="1"/>
       <c r="AW37" s="1"/>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>70</v>
       </c>
@@ -4678,7 +4709,7 @@
         <v>11.8</v>
       </c>
       <c r="Q38" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>82.200000000000017</v>
       </c>
       <c r="R38" s="5">
@@ -4746,7 +4777,7 @@
       <c r="AV38" s="1"/>
       <c r="AW38" s="1"/>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>71</v>
       </c>
@@ -4832,7 +4863,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG39" s="1"/>
+      <c r="AG39" s="1">
+        <f t="shared" ref="AG39:AG42" si="11">F39*G39</f>
+        <v>108.17999999999999</v>
+      </c>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
@@ -4936,7 +4970,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG40" s="1"/>
+      <c r="AG40" s="16">
+        <f t="shared" si="11"/>
+        <v>299.07299999999998</v>
+      </c>
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
@@ -5042,7 +5079,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG41" s="1"/>
+      <c r="AG41" s="16">
+        <f t="shared" si="11"/>
+        <v>117.931</v>
+      </c>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
@@ -5060,7 +5100,7 @@
       <c r="AV41" s="1"/>
       <c r="AW41" s="1"/>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>74</v>
       </c>
@@ -5148,7 +5188,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG42" s="1"/>
+      <c r="AG42" s="1">
+        <f t="shared" si="11"/>
+        <v>237.976</v>
+      </c>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
@@ -5166,7 +5209,7 @@
       <c r="AV42" s="1"/>
       <c r="AW42" s="1"/>
     </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>75</v>
       </c>
@@ -5358,7 +5401,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG44" s="1"/>
+      <c r="AG44" s="1">
+        <f t="shared" ref="AG44:AG45" si="12">F44*G44</f>
+        <v>23.6</v>
+      </c>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
@@ -5376,7 +5422,7 @@
       <c r="AV44" s="1"/>
       <c r="AW44" s="1"/>
     </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>77</v>
       </c>
@@ -5464,7 +5510,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG45" s="1"/>
+      <c r="AG45" s="1">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
@@ -5482,7 +5531,7 @@
       <c r="AV45" s="1"/>
       <c r="AW45" s="1"/>
     </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>78</v>
       </c>
@@ -5592,7 +5641,7 @@
       <c r="AV46" s="1"/>
       <c r="AW46" s="1"/>
     </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>79</v>
       </c>
@@ -5693,7 +5742,7 @@
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
     </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>81</v>
       </c>
@@ -5801,7 +5850,7 @@
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
     </row>
-    <row r="49" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>82</v>
       </c>
@@ -5909,7 +5958,7 @@
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
     </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>83</v>
       </c>
@@ -6010,7 +6059,7 @@
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
     </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>84</v>
       </c>
@@ -6201,7 +6250,10 @@
         <f>G52*Q52</f>
         <v>0</v>
       </c>
-      <c r="AG52" s="1"/>
+      <c r="AG52" s="16">
+        <f>F52*G52</f>
+        <v>132.386</v>
+      </c>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
@@ -29116,7 +29168,22 @@
       <c r="AW500" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AF53" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AF53" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="18">
+      <filters>
+        <filter val="#ДЕЛ/0!"/>
+        <filter val="151"/>
+        <filter val="35"/>
+        <filter val="39"/>
+        <filter val="41"/>
+        <filter val="43"/>
+        <filter val="47"/>
+        <filter val="63"/>
+        <filter val="71"/>
+        <filter val="74"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
